--- a/public/downloads/06_DCF評価モデル.xlsx
+++ b/public/downloads/06_DCF評価モデル.xlsx
@@ -7,26 +7,26 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="16000" windowHeight="9000" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Cover" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Inputs" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="Assumptions" state="visible" r:id="rId6"/>
+    <sheet sheetId="1" name="表紙" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="入力" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="前提" state="visible" r:id="rId6"/>
     <sheet sheetId="4" name="PL" state="visible" r:id="rId7"/>
     <sheet sheetId="5" name="BS" state="visible" r:id="rId8"/>
     <sheet sheetId="6" name="CF" state="visible" r:id="rId9"/>
-    <sheet sheetId="7" name="Schedules" state="visible" r:id="rId10"/>
+    <sheet sheetId="7" name="計算明細" state="visible" r:id="rId10"/>
     <sheet sheetId="8" name="DCF" state="visible" r:id="rId11"/>
-    <sheet sheetId="9" name="Checks" state="visible" r:id="rId12"/>
+    <sheet sheetId="9" name="チェック" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Cover'!$A1:$F15</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Inputs'!$A1:$F25</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Assumptions'!$A1:$C12</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'表紙'!$A1:$F15</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'入力'!$A1:$F25</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'前提'!$A1:$C12</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'PL'!$A1:$F9</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'BS'!$A1:$F15</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'CF'!$A1:$F11</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'Schedules'!$A1:$F10</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'計算明細'!$A1:$F10</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'DCF'!$A1:$G30</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="8">'Checks'!$A1:$D11</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">'チェック'!$A1:$D11</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
@@ -35,244 +35,247 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="98">
   <si>
-    <t>DCF Valuation Model</t>
-  </si>
-  <si>
-    <t>Educational sample | Shared DCF case | Unit: JPY million</t>
-  </si>
-  <si>
-    <t>Model status</t>
-  </si>
-  <si>
-    <t>Calculation integrity</t>
-  </si>
-  <si>
-    <t>Decision readiness</t>
-  </si>
-  <si>
-    <t>Valuation convention</t>
-  </si>
-  <si>
-    <t>Period-end convention: each forecast year-end / 1–5 periods</t>
-  </si>
-  <si>
-    <t>Use caution</t>
-  </si>
-  <si>
-    <t>Inputs are an educational case, not live market data. Review sources and assumptions before any real transaction use.</t>
-  </si>
-  <si>
-    <t>Inputs</t>
-  </si>
-  <si>
-    <t>Blue cells are editable. Forecasts and valuation inputs come from the shared DCF educational case.</t>
-  </si>
-  <si>
-    <t>Operating forecast</t>
-  </si>
-  <si>
-    <t>FY2026</t>
-  </si>
-  <si>
-    <t>FY2027</t>
-  </si>
-  <si>
-    <t>FY2028</t>
-  </si>
-  <si>
-    <t>FY2029</t>
-  </si>
-  <si>
-    <t>FY2030</t>
-  </si>
-  <si>
-    <t>Revenue</t>
+    <t>DCF Valuationモデル</t>
+  </si>
+  <si>
+    <t>教育用サンプル｜共通DCFケース｜単位：百万円</t>
+  </si>
+  <si>
+    <t>モデルの状態</t>
+  </si>
+  <si>
+    <t>計算整合性</t>
+  </si>
+  <si>
+    <t>意思決定への利用可否</t>
+  </si>
+  <si>
+    <t>Valuationの基準</t>
+  </si>
+  <si>
+    <t>各予測年度末を基準とする期末割引（1～5期間）</t>
+  </si>
+  <si>
+    <t>利用上の注意</t>
+  </si>
+  <si>
+    <t>入力値は教育用の仮定であり、市場データではありません。実案件で利用する前に出所、基準日、前提条件を確認してください。</t>
+  </si>
+  <si>
+    <t>入力</t>
+  </si>
+  <si>
+    <t>青字セルが手入力欄です。事業計画、WACC、永久成長率、ネット有利子負債調整を入力します。</t>
+  </si>
+  <si>
+    <t>事業計画</t>
+  </si>
+  <si>
+    <t>2026年度</t>
+  </si>
+  <si>
+    <t>2027年度</t>
+  </si>
+  <si>
+    <t>2028年度</t>
+  </si>
+  <si>
+    <t>2029年度</t>
+  </si>
+  <si>
+    <t>2030年度</t>
+  </si>
+  <si>
+    <t>売上高</t>
   </si>
   <si>
     <t>EBIT</t>
   </si>
   <si>
-    <t>Tax Rate</t>
-  </si>
-  <si>
-    <t>D&amp;A</t>
-  </si>
-  <si>
-    <t>Capex</t>
-  </si>
-  <si>
-    <t>Increase in NWC</t>
-  </si>
-  <si>
-    <t>Valuation and bridge inputs</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Risk-free Rate</t>
-  </si>
-  <si>
-    <t>Equity Risk Premium</t>
-  </si>
-  <si>
-    <t>Beta</t>
-  </si>
-  <si>
-    <t>Pre-tax Cost of Debt</t>
-  </si>
-  <si>
-    <t>Equity Weight</t>
-  </si>
-  <si>
-    <t>Debt Weight</t>
-  </si>
-  <si>
-    <t>Terminal Growth</t>
-  </si>
-  <si>
-    <t>Cash</t>
-  </si>
-  <si>
-    <t>Debt</t>
-  </si>
-  <si>
-    <t>Debt-like Items</t>
-  </si>
-  <si>
-    <t>Non-controlling Interests</t>
-  </si>
-  <si>
-    <t>Assumptions</t>
-  </si>
-  <si>
-    <t>Formula-driven WACC and valuation convention. WACC must exceed terminal growth.</t>
-  </si>
-  <si>
-    <t>Assumption / calculation</t>
-  </si>
-  <si>
-    <t>Definition / review</t>
-  </si>
-  <si>
-    <t>Period-end convention</t>
-  </si>
-  <si>
-    <t>Each forecast year-end / 1–5 periods</t>
-  </si>
-  <si>
-    <t>Cost of Equity</t>
-  </si>
-  <si>
-    <t>Risk-free Rate + Beta × Equity Risk Premium</t>
-  </si>
-  <si>
-    <t>After-tax Cost of Debt</t>
-  </si>
-  <si>
-    <t>Pre-tax Cost of Debt × (1 − Tax Rate)</t>
-  </si>
-  <si>
-    <t>Capital Weights Sum</t>
-  </si>
-  <si>
-    <t>Must equal 100.0%</t>
+    <t>税率</t>
+  </si>
+  <si>
+    <t>減価償却費</t>
+  </si>
+  <si>
+    <t>設備投資</t>
+  </si>
+  <si>
+    <t>運転資本増加</t>
+  </si>
+  <si>
+    <t>Valuation・株主価値調整の入力</t>
+  </si>
+  <si>
+    <t>入力値</t>
+  </si>
+  <si>
+    <t>リスクフリーレート</t>
+  </si>
+  <si>
+    <t>株式リスクプレミアム</t>
+  </si>
+  <si>
+    <t>ベータ</t>
+  </si>
+  <si>
+    <t>税引前負債コスト</t>
+  </si>
+  <si>
+    <t>株主資本構成比</t>
+  </si>
+  <si>
+    <t>有利子負債構成比</t>
+  </si>
+  <si>
+    <t>永久成長率</t>
+  </si>
+  <si>
+    <t>現金及び現金同等物</t>
+  </si>
+  <si>
+    <t>有利子負債</t>
+  </si>
+  <si>
+    <t>有利子負債類似項目</t>
+  </si>
+  <si>
+    <t>非支配持分</t>
+  </si>
+  <si>
+    <t>前提</t>
+  </si>
+  <si>
+    <t>WACCとValuationの基準を数式で集約します。WACCが永久成長率を上回ることを確認します。</t>
+  </si>
+  <si>
+    <t>前提・計算項目</t>
+  </si>
+  <si>
+    <t>計算値</t>
+  </si>
+  <si>
+    <t>定義・確認事項</t>
+  </si>
+  <si>
+    <t>期末割引</t>
+  </si>
+  <si>
+    <t>各予測年度末を基準とする1～5期間</t>
+  </si>
+  <si>
+    <t>株主資本コスト</t>
+  </si>
+  <si>
+    <t>リスクフリーレート + ベータ × 株式リスクプレミアム</t>
+  </si>
+  <si>
+    <t>税引後負債コスト</t>
+  </si>
+  <si>
+    <t>税引前負債コスト ×（1 − 税率）</t>
+  </si>
+  <si>
+    <t>資本構成比合計</t>
+  </si>
+  <si>
+    <t>100.0%となること</t>
   </si>
   <si>
     <t>WACC</t>
   </si>
   <si>
-    <t>Equity Weight × CoE + Debt Weight × After-tax CoD</t>
-  </si>
-  <si>
-    <t>WACC &gt; g required</t>
+    <t>株主資本構成比 × 株主資本コスト + 有利子負債構成比 × 税引後負債コスト</t>
+  </si>
+  <si>
+    <t>WACCが永久成長率を上回ること</t>
   </si>
   <si>
     <t>PL</t>
   </si>
   <si>
-    <t>Forecast operating results linked to Inputs. Unit: JPY million.</t>
-  </si>
-  <si>
-    <t>Metric</t>
-  </si>
-  <si>
-    <t>Tax on EBIT</t>
-  </si>
-  <si>
-    <t>NOPAT</t>
+    <t>入力シートに連動する予測損益計算書です。単位：百万円。</t>
+  </si>
+  <si>
+    <t>項目</t>
+  </si>
+  <si>
+    <t>営業利益に係る税金</t>
+  </si>
+  <si>
+    <t>税引後営業利益</t>
   </si>
   <si>
     <t>BS</t>
   </si>
   <si>
-    <t>Valuation-date balance sheet references and forecast working-capital movement. Unit: JPY million.</t>
-  </si>
-  <si>
-    <t>Valuation-date bridge item</t>
-  </si>
-  <si>
-    <t>Amount</t>
-  </si>
-  <si>
-    <t>Treatment</t>
-  </si>
-  <si>
-    <t>Add to EV</t>
-  </si>
-  <si>
-    <t>Deduct from EV</t>
+    <t>評価基準日の株主価値調整項目と予測運転資本増加を整理します。単位：百万円。</t>
+  </si>
+  <si>
+    <t>評価基準日の調整項目</t>
+  </si>
+  <si>
+    <t>金額</t>
+  </si>
+  <si>
+    <t>調整方法</t>
+  </si>
+  <si>
+    <t>Enterprise Valueに加算</t>
+  </si>
+  <si>
+    <t>Enterprise Valueから控除</t>
   </si>
   <si>
     <t>CF</t>
   </si>
   <si>
-    <t>FCFF is calculated from EBIT after tax, D&amp;A, Capex and Increase in NWC. Unit: JPY million.</t>
+    <t>FCFF（企業向けフリーキャッシュフロー）を税引後営業利益、減価償却費、設備投資、運転資本増加から計算します。単位：百万円。</t>
   </si>
   <si>
     <t>FCFF</t>
   </si>
   <si>
-    <t>Schedules</t>
-  </si>
-  <si>
-    <t>Operating schedules and period-end discount factors. Unit: JPY million unless stated.</t>
-  </si>
-  <si>
-    <t>Schedule</t>
+    <t>計算明細</t>
+  </si>
+  <si>
+    <t>設備投資、運転資本、割引係数の計算明細です。記載がない限り単位：百万円。</t>
+  </si>
+  <si>
+    <t>計算項目</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>Discount Period</t>
-  </si>
-  <si>
-    <t>Discount Factor</t>
+    <t>割引期間</t>
+  </si>
+  <si>
+    <t>割引係数</t>
   </si>
   <si>
     <t>DCF</t>
   </si>
   <si>
-    <t>Period-end DCF valuation, EV-to-Equity bridge and 5×5 WACC–growth sensitivity. Unit: JPY million.</t>
+    <t>期末割引によるValuation、Enterprise ValueからEquity Valueへの調整、WACC・永久成長率の感応度分析です。単位：百万円。</t>
   </si>
   <si>
     <t>Valuation</t>
   </si>
   <si>
-    <t>PV of FCFF</t>
-  </si>
-  <si>
-    <t>PV of Explicit FCFF</t>
+    <t>FCFFの現在価値</t>
+  </si>
+  <si>
+    <t>明示予測期間のFCFF現在価値</t>
   </si>
   <si>
     <t>FCFF (n+1)</t>
   </si>
   <si>
-    <t>Terminal Value</t>
-  </si>
-  <si>
-    <t>PV of Terminal Value</t>
+    <t>継続価値</t>
+  </si>
+  <si>
+    <t>継続価値の現在価値</t>
   </si>
   <si>
     <t>Enterprise Value</t>
@@ -281,52 +284,49 @@
     <t>Equity Value</t>
   </si>
   <si>
-    <t>Enterprise Value Sensitivity</t>
+    <t>Enterprise Value 感応度分析</t>
   </si>
   <si>
     <t>WACC / g</t>
   </si>
   <si>
-    <t>Checks</t>
-  </si>
-  <si>
-    <t>Formula-driven model checks. Calculation integrity is distinct from decision readiness.</t>
-  </si>
-  <si>
-    <t>Check</t>
-  </si>
-  <si>
-    <t>Formula result</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Purpose</t>
-  </si>
-  <si>
-    <t>Capital weights sum</t>
-  </si>
-  <si>
-    <t>Equity and debt weights must total 100%.</t>
-  </si>
-  <si>
-    <t>WACC &gt; Terminal Growth</t>
-  </si>
-  <si>
-    <t>Gordon Growth denominator must remain positive.</t>
-  </si>
-  <si>
-    <t>EV bridge</t>
-  </si>
-  <si>
-    <t>Equity Value must reconcile to Enterprise Value adjustments.</t>
-  </si>
-  <si>
-    <t>Formula-error count</t>
-  </si>
-  <si>
-    <t>Counts formula errors in core calculation ranges.</t>
+    <t>チェック</t>
+  </si>
+  <si>
+    <t>数式で計算整合性を確認します。計算が合うことと、意思決定に使えることは別に判定します。</t>
+  </si>
+  <si>
+    <t>チェック項目</t>
+  </si>
+  <si>
+    <t>計算結果</t>
+  </si>
+  <si>
+    <t>判定</t>
+  </si>
+  <si>
+    <t>確認目的</t>
+  </si>
+  <si>
+    <t>株主資本と有利子負債の構成比が100%となること。</t>
+  </si>
+  <si>
+    <t>WACCと永久成長率</t>
+  </si>
+  <si>
+    <t>継続価値の分母が正となること。</t>
+  </si>
+  <si>
+    <t>株主価値への調整</t>
+  </si>
+  <si>
+    <t>Equity ValueがEnterprise Valueからの調整に一致すること。</t>
+  </si>
+  <si>
+    <t>数式エラー件数</t>
+  </si>
+  <si>
+    <t>主要計算範囲に数式エラーがないこと。</t>
   </si>
 </sst>
 </file>
@@ -912,8 +912,8 @@
         <v>3</v>
       </c>
       <c r="C5" s="5" t="str">
-        <f>Checks!B10</f>
-        <v>OK</v>
+        <f>チェック!B10</f>
+        <v>適合</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
@@ -921,8 +921,8 @@
         <v>4</v>
       </c>
       <c r="C6" s="6" t="str">
-        <f>Checks!B11</f>
-        <v>Educational sample / source review required</v>
+        <f>チェック!B11</f>
+        <v>教育用サンプル・出所確認が必要</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.25">
@@ -1277,10 +1277,10 @@
         <v>38</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1288,10 +1288,10 @@
         <v>5</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1306,50 +1306,50 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B8" s="12">
-        <f>Inputs!B14+Inputs!B16*Inputs!B15</f>
+        <f>入力!B14+入力!B16*入力!B15</f>
         <v>0.081</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B9" s="12">
-        <f>Inputs!B17*(1-Inputs!B18)</f>
+        <f>入力!B17*(1-入力!B18)</f>
         <v>0.017499999999999998</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B10" s="12">
-        <f>Inputs!B19+Inputs!B20</f>
+        <f>入力!B19+入力!B20</f>
         <v>1</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B11" s="13">
-        <f>Inputs!B19*B8+Inputs!B20*B9</f>
+        <f>入力!B19*B8+入力!B20*B9</f>
         <v>0.065125</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -1357,11 +1357,11 @@
         <v>31</v>
       </c>
       <c r="B12" s="12">
-        <f>Inputs!B21</f>
+        <f>入力!B21</f>
         <v>0.015</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -1388,7 +1388,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1398,7 +1398,7 @@
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -1408,7 +1408,7 @@
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>12</v>
@@ -1431,23 +1431,23 @@
         <v>17</v>
       </c>
       <c r="B5" s="14">
-        <f>Inputs!B5</f>
+        <f>入力!B5</f>
         <v>1100</v>
       </c>
       <c r="C5" s="14">
-        <f>Inputs!C5</f>
+        <f>入力!C5</f>
         <v>1200</v>
       </c>
       <c r="D5" s="14">
-        <f>Inputs!D5</f>
+        <f>入力!D5</f>
         <v>1320</v>
       </c>
       <c r="E5" s="14">
-        <f>Inputs!E5</f>
+        <f>入力!E5</f>
         <v>1452</v>
       </c>
       <c r="F5" s="14">
-        <f>Inputs!F5</f>
+        <f>入力!F5</f>
         <v>1597.2</v>
       </c>
     </row>
@@ -1456,23 +1456,23 @@
         <v>18</v>
       </c>
       <c r="B6" s="14">
-        <f>Inputs!B6</f>
+        <f>入力!B6</f>
         <v>120</v>
       </c>
       <c r="C6" s="14">
-        <f>Inputs!C6</f>
+        <f>入力!C6</f>
         <v>140</v>
       </c>
       <c r="D6" s="14">
-        <f>Inputs!D6</f>
+        <f>入力!D6</f>
         <v>160</v>
       </c>
       <c r="E6" s="14">
-        <f>Inputs!E6</f>
+        <f>入力!E6</f>
         <v>180</v>
       </c>
       <c r="F6" s="14">
-        <f>Inputs!F6</f>
+        <f>入力!F6</f>
         <v>200</v>
       </c>
     </row>
@@ -1481,29 +1481,29 @@
         <v>19</v>
       </c>
       <c r="B7" s="12">
-        <f>Inputs!B7</f>
+        <f>入力!B7</f>
         <v>0.3</v>
       </c>
       <c r="C7" s="12">
-        <f>Inputs!C7</f>
+        <f>入力!C7</f>
         <v>0.3</v>
       </c>
       <c r="D7" s="12">
-        <f>Inputs!D7</f>
+        <f>入力!D7</f>
         <v>0.3</v>
       </c>
       <c r="E7" s="12">
-        <f>Inputs!E7</f>
+        <f>入力!E7</f>
         <v>0.3</v>
       </c>
       <c r="F7" s="12">
-        <f>Inputs!F7</f>
+        <f>入力!F7</f>
         <v>0.3</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B8" s="14">
         <f>-B6*B7</f>
@@ -1528,7 +1528,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B9" s="14">
         <f>B6+B8</f>
@@ -1575,7 +1575,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1585,7 +1585,7 @@
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -1595,13 +1595,13 @@
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1609,11 +1609,11 @@
         <v>32</v>
       </c>
       <c r="B5" s="14">
-        <f>Inputs!B22</f>
+        <f>入力!B22</f>
         <v>100</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1621,11 +1621,11 @@
         <v>33</v>
       </c>
       <c r="B6" s="14">
-        <f>Inputs!B23</f>
+        <f>入力!B23</f>
         <v>350</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -1633,11 +1633,11 @@
         <v>34</v>
       </c>
       <c r="B7" s="14">
-        <f>Inputs!B24</f>
+        <f>入力!B24</f>
         <v>20</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -1645,11 +1645,11 @@
         <v>35</v>
       </c>
       <c r="B8" s="14">
-        <f>Inputs!B25</f>
+        <f>入力!B25</f>
         <v>10</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1675,23 +1675,23 @@
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
       <c r="B12" s="14">
-        <f>Inputs!B10</f>
+        <f>入力!B10</f>
         <v>7.2</v>
       </c>
       <c r="C12" s="14">
-        <f>Inputs!C10</f>
+        <f>入力!C10</f>
         <v>6.9</v>
       </c>
       <c r="D12" s="14">
-        <f>Inputs!D10</f>
+        <f>入力!D10</f>
         <v>7.9</v>
       </c>
       <c r="E12" s="14">
-        <f>Inputs!E10</f>
+        <f>入力!E10</f>
         <v>9.5</v>
       </c>
       <c r="F12" s="14">
-        <f>Inputs!F10</f>
+        <f>入力!F10</f>
         <v>7.7</v>
       </c>
     </row>
@@ -1719,7 +1719,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1729,7 +1729,7 @@
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -1739,7 +1739,7 @@
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>12</v>
@@ -1787,29 +1787,29 @@
         <v>19</v>
       </c>
       <c r="B6" s="12">
-        <f>Inputs!B7</f>
+        <f>入力!B7</f>
         <v>0.3</v>
       </c>
       <c r="C6" s="12">
-        <f>Inputs!C7</f>
+        <f>入力!C7</f>
         <v>0.3</v>
       </c>
       <c r="D6" s="12">
-        <f>Inputs!D7</f>
+        <f>入力!D7</f>
         <v>0.3</v>
       </c>
       <c r="E6" s="12">
-        <f>Inputs!E7</f>
+        <f>入力!E7</f>
         <v>0.3</v>
       </c>
       <c r="F6" s="12">
-        <f>Inputs!F7</f>
+        <f>入力!F7</f>
         <v>0.3</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B7" s="14">
         <f>B5*(1-B6)</f>
@@ -1837,23 +1837,23 @@
         <v>20</v>
       </c>
       <c r="B8" s="14">
-        <f>Inputs!B8</f>
+        <f>入力!B8</f>
         <v>30</v>
       </c>
       <c r="C8" s="14">
-        <f>Inputs!C8</f>
+        <f>入力!C8</f>
         <v>32</v>
       </c>
       <c r="D8" s="14">
-        <f>Inputs!D8</f>
+        <f>入力!D8</f>
         <v>34</v>
       </c>
       <c r="E8" s="14">
-        <f>Inputs!E8</f>
+        <f>入力!E8</f>
         <v>36</v>
       </c>
       <c r="F8" s="14">
-        <f>Inputs!F8</f>
+        <f>入力!F8</f>
         <v>38</v>
       </c>
     </row>
@@ -1862,23 +1862,23 @@
         <v>21</v>
       </c>
       <c r="B9" s="14">
-        <f>Inputs!B9</f>
+        <f>入力!B9</f>
         <v>30</v>
       </c>
       <c r="C9" s="14">
-        <f>Inputs!C9</f>
+        <f>入力!C9</f>
         <v>32</v>
       </c>
       <c r="D9" s="14">
-        <f>Inputs!D9</f>
+        <f>入力!D9</f>
         <v>34</v>
       </c>
       <c r="E9" s="14">
-        <f>Inputs!E9</f>
+        <f>入力!E9</f>
         <v>36</v>
       </c>
       <c r="F9" s="14">
-        <f>Inputs!F9</f>
+        <f>入力!F9</f>
         <v>38</v>
       </c>
     </row>
@@ -1887,29 +1887,29 @@
         <v>22</v>
       </c>
       <c r="B10" s="14">
-        <f>Inputs!B10</f>
+        <f>入力!B10</f>
         <v>7.2</v>
       </c>
       <c r="C10" s="14">
-        <f>Inputs!C10</f>
+        <f>入力!C10</f>
         <v>6.9</v>
       </c>
       <c r="D10" s="14">
-        <f>Inputs!D10</f>
+        <f>入力!D10</f>
         <v>7.9</v>
       </c>
       <c r="E10" s="14">
-        <f>Inputs!E10</f>
+        <f>入力!E10</f>
         <v>9.5</v>
       </c>
       <c r="F10" s="14">
-        <f>Inputs!F10</f>
+        <f>入力!F10</f>
         <v>7.7</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B11" s="15">
         <f>B5*(1-B6)+B8-B9-B10</f>
@@ -1956,7 +1956,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1966,7 +1966,7 @@
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -1976,7 +1976,7 @@
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>12</v>
@@ -1999,23 +1999,23 @@
         <v>20</v>
       </c>
       <c r="B5" s="14">
-        <f>Inputs!B8</f>
+        <f>入力!B8</f>
         <v>30</v>
       </c>
       <c r="C5" s="14">
-        <f>Inputs!C8</f>
+        <f>入力!C8</f>
         <v>32</v>
       </c>
       <c r="D5" s="14">
-        <f>Inputs!D8</f>
+        <f>入力!D8</f>
         <v>34</v>
       </c>
       <c r="E5" s="14">
-        <f>Inputs!E8</f>
+        <f>入力!E8</f>
         <v>36</v>
       </c>
       <c r="F5" s="14">
-        <f>Inputs!F8</f>
+        <f>入力!F8</f>
         <v>38</v>
       </c>
     </row>
@@ -2024,23 +2024,23 @@
         <v>21</v>
       </c>
       <c r="B6" s="14">
-        <f>Inputs!B9</f>
+        <f>入力!B9</f>
         <v>30</v>
       </c>
       <c r="C6" s="14">
-        <f>Inputs!C9</f>
+        <f>入力!C9</f>
         <v>32</v>
       </c>
       <c r="D6" s="14">
-        <f>Inputs!D9</f>
+        <f>入力!D9</f>
         <v>34</v>
       </c>
       <c r="E6" s="14">
-        <f>Inputs!E9</f>
+        <f>入力!E9</f>
         <v>36</v>
       </c>
       <c r="F6" s="14">
-        <f>Inputs!F9</f>
+        <f>入力!F9</f>
         <v>38</v>
       </c>
     </row>
@@ -2049,29 +2049,29 @@
         <v>22</v>
       </c>
       <c r="B7" s="14">
-        <f>Inputs!B10</f>
+        <f>入力!B10</f>
         <v>7.2</v>
       </c>
       <c r="C7" s="14">
-        <f>Inputs!C10</f>
+        <f>入力!C10</f>
         <v>6.9</v>
       </c>
       <c r="D7" s="14">
-        <f>Inputs!D10</f>
+        <f>入力!D10</f>
         <v>7.9</v>
       </c>
       <c r="E7" s="14">
-        <f>Inputs!E10</f>
+        <f>入力!E10</f>
         <v>9.5</v>
       </c>
       <c r="F7" s="14">
-        <f>Inputs!F10</f>
+        <f>入力!F10</f>
         <v>7.7</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -2081,7 +2081,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B9" s="4">
         <v>1</v>
@@ -2101,26 +2101,26 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B10" s="16">
-        <f>1/(1+Assumptions!$B$11)^B9</f>
+        <f>1/(1+前提!$B$11)^B9</f>
         <v>0.9388569416735124</v>
       </c>
       <c r="C10" s="16">
-        <f>1/(1+Assumptions!$B$11)^C9</f>
+        <f>1/(1+前提!$B$11)^C9</f>
         <v>0.8814523569285412</v>
       </c>
       <c r="D10" s="16">
-        <f>1/(1+Assumptions!$B$11)^D9</f>
+        <f>1/(1+前提!$B$11)^D9</f>
         <v>0.8275576640568393</v>
       </c>
       <c r="E10" s="16">
-        <f>1/(1+Assumptions!$B$11)^E9</f>
+        <f>1/(1+前提!$B$11)^E9</f>
         <v>0.7769582575348801</v>
       </c>
       <c r="F10" s="16">
-        <f>1/(1+Assumptions!$B$11)^F9</f>
+        <f>1/(1+前提!$B$11)^F9</f>
         <v>0.7294526534771788</v>
       </c>
     </row>
@@ -2148,7 +2148,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2159,7 +2159,7 @@
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2170,7 +2170,7 @@
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>12</v>
@@ -2190,7 +2190,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B5" s="14">
         <f>CF!B11</f>
@@ -2215,32 +2215,32 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B6" s="16">
-        <f>Schedules!B10</f>
+        <f>計算明細!B10</f>
         <v>0.9388569416735124</v>
       </c>
       <c r="C6" s="16">
-        <f>Schedules!C10</f>
+        <f>計算明細!C10</f>
         <v>0.8814523569285412</v>
       </c>
       <c r="D6" s="16">
-        <f>Schedules!D10</f>
+        <f>計算明細!D10</f>
         <v>0.8275576640568393</v>
       </c>
       <c r="E6" s="16">
-        <f>Schedules!E10</f>
+        <f>計算明細!E10</f>
         <v>0.7769582575348801</v>
       </c>
       <c r="F6" s="16">
-        <f>Schedules!F10</f>
+        <f>計算明細!F10</f>
         <v>0.7294526534771788</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B7" s="14">
         <f>B5*B6</f>
@@ -2265,7 +2265,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B10" s="14">
         <f>SUM(B7:F7)</f>
@@ -2274,25 +2274,25 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B11" s="14">
-        <f>F5*(1+Assumptions!$B$12)</f>
+        <f>F5*(1+前提!$B$12)</f>
         <v>134.2845</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B12" s="14">
-        <f>IF(Assumptions!$B$11&lt;=Assumptions!$B$12,NA(),B11/(Assumptions!$B$11-Assumptions!$B$12))</f>
+        <f>IF(前提!$B$11&lt;=前提!$B$12,NA(),B11/(前提!$B$11-前提!$B$12))</f>
         <v>2678.992518703242</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B13" s="14">
         <f>B12*F6</f>
@@ -2301,7 +2301,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B14" s="17">
         <f>B10+B13</f>
@@ -2317,7 +2317,7 @@
         <v>32</v>
       </c>
       <c r="B16" s="14">
-        <f>Inputs!B22</f>
+        <f>入力!B22</f>
         <v>100</v>
       </c>
     </row>
@@ -2326,7 +2326,7 @@
         <v>33</v>
       </c>
       <c r="B17" s="14">
-        <f>Inputs!B23</f>
+        <f>入力!B23</f>
         <v>350</v>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
         <v>34</v>
       </c>
       <c r="B18" s="14">
-        <f>Inputs!B24</f>
+        <f>入力!B24</f>
         <v>20</v>
       </c>
     </row>
@@ -2344,13 +2344,13 @@
         <v>35</v>
       </c>
       <c r="B19" s="14">
-        <f>Inputs!B25</f>
+        <f>入力!B25</f>
         <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B20" s="17">
         <f>B14+B16-B17-B18-B19</f>
@@ -2359,12 +2359,12 @@
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B25" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C25" s="18">
         <v>0.005</v>
@@ -2533,7 +2533,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2541,7 +2541,7 @@
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2549,29 +2549,29 @@
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>90</v>
+        <v>47</v>
       </c>
       <c r="B5" s="12">
-        <f>Inputs!B19+Inputs!B20</f>
+        <f>入力!B19+入力!B20</f>
         <v>1</v>
       </c>
       <c r="C5" s="20" t="str">
-        <f>IF(ABS(B5-1)&lt;0.000001,"OK","ERROR")</f>
-        <v>OK</v>
+        <f>IF(ABS(B5-1)&lt;0.000001,"適合","要確認")</f>
+        <v>適合</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>91</v>
@@ -2582,12 +2582,12 @@
         <v>92</v>
       </c>
       <c r="B6" s="21" t="b">
-        <f>Assumptions!B11&gt;Assumptions!B12</f>
+        <f>前提!B11&gt;前提!B12</f>
         <v>1</v>
       </c>
       <c r="C6" s="20" t="str">
-        <f>IF(B6,"OK","ERROR")</f>
-        <v>OK</v>
+        <f>IF(B6,"適合","要確認")</f>
+        <v>適合</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>93</v>
@@ -2602,8 +2602,8 @@
         <v>0</v>
       </c>
       <c r="C7" s="20" t="str">
-        <f>IF(ABS(B7)&lt;0.000001,"OK","ERROR")</f>
-        <v>OK</v>
+        <f>IF(ABS(B7)&lt;0.000001,"適合","要確認")</f>
+        <v>適合</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>95</v>
@@ -2614,12 +2614,12 @@
         <v>96</v>
       </c>
       <c r="B8" s="23">
-        <f>SUMPRODUCT(--ISERROR(Assumptions!B8:B12))+SUMPRODUCT(--ISERROR(PL!B5:F9))+SUMPRODUCT(--ISERROR(BS!B5:F12))+SUMPRODUCT(--ISERROR(CF!B5:F11))+SUMPRODUCT(--ISERROR(Schedules!B5:F10))+SUMPRODUCT(--ISERROR(DCF!B5:G30))</f>
+        <f>SUMPRODUCT(--ISERROR(前提!B8:B12))+SUMPRODUCT(--ISERROR(PL!B5:F9))+SUMPRODUCT(--ISERROR(BS!B5:F12))+SUMPRODUCT(--ISERROR(CF!B5:F11))+SUMPRODUCT(--ISERROR(計算明細!B5:F10))+SUMPRODUCT(--ISERROR(DCF!B5:G30))</f>
         <v>0</v>
       </c>
       <c r="C8" s="20" t="str">
-        <f>IF(B8=0,"OK","ERROR")</f>
-        <v>OK</v>
+        <f>IF(B8=0,"適合","要確認")</f>
+        <v>適合</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>97</v>
@@ -2636,8 +2636,8 @@
         <v>3</v>
       </c>
       <c r="B10" s="20" t="str">
-        <f>IF(COUNTIF(C5:C8,"&lt;&gt;OK")=0,"OK","ERROR")</f>
-        <v>OK</v>
+        <f>IF(COUNTIF(C5:C8,"&lt;&gt;適合")=0,"適合","要確認")</f>
+        <v>適合</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
@@ -2647,8 +2647,8 @@
         <v>4</v>
       </c>
       <c r="B11" s="21" t="str">
-        <f>"Educational sample / source review required"</f>
-        <v>Educational sample / source review required</v>
+        <f>"教育用サンプル・出所確認が必要"</f>
+        <v>教育用サンプル・出所確認が必要</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
